--- a/VerveStacks_TJK_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_TJK_grids/Sets-vervestacks.xlsx
@@ -5,16 +5,17 @@
   <workbookPr updateLinks="never" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\assumptions\VerveStacks_ISO_template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_TJK_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52485F27-B929-4917-B544-8B3D23B3A785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E707103E-4326-4CF5-B3FD-BFB11F0A027E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
-    <sheet name="VEDA_Sets-Proc" sheetId="1" r:id="rId2"/>
+    <sheet name="geo_sets" sheetId="3" r:id="rId2"/>
+    <sheet name="VEDA_Sets-Proc" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="160">
   <si>
     <t>~TFM_Psets</t>
   </si>
@@ -331,6 +332,192 @@
   </si>
   <si>
     <t>distr*</t>
+  </si>
+  <si>
+    <t>~tfm_psets</t>
+  </si>
+  <si>
+    <t>setname</t>
+  </si>
+  <si>
+    <t>pset_co</t>
+  </si>
+  <si>
+    <t>pset_ci</t>
+  </si>
+  <si>
+    <t>t_pos_andor</t>
+  </si>
+  <si>
+    <t>p_w242159365</t>
+  </si>
+  <si>
+    <t>e_w242159365*</t>
+  </si>
+  <si>
+    <t>OR</t>
+  </si>
+  <si>
+    <t>p_w488077624</t>
+  </si>
+  <si>
+    <t>e_w488077624*</t>
+  </si>
+  <si>
+    <t>p_w799346816</t>
+  </si>
+  <si>
+    <t>e_w799346816*</t>
+  </si>
+  <si>
+    <t>p_w1016951696</t>
+  </si>
+  <si>
+    <t>e_w1016951696*</t>
+  </si>
+  <si>
+    <t>p_w1373384046</t>
+  </si>
+  <si>
+    <t>e_w1373384046*</t>
+  </si>
+  <si>
+    <t>p_TJ6</t>
+  </si>
+  <si>
+    <t>e_TJ6*</t>
+  </si>
+  <si>
+    <t>p_TJ29</t>
+  </si>
+  <si>
+    <t>e_TJ29*</t>
+  </si>
+  <si>
+    <t>p_TJ20</t>
+  </si>
+  <si>
+    <t>e_TJ20*</t>
+  </si>
+  <si>
+    <t>p_TJ46</t>
+  </si>
+  <si>
+    <t>e_TJ46*</t>
+  </si>
+  <si>
+    <t>p_TJ30</t>
+  </si>
+  <si>
+    <t>e_TJ30*</t>
+  </si>
+  <si>
+    <t>p_TJ4</t>
+  </si>
+  <si>
+    <t>e_TJ4*</t>
+  </si>
+  <si>
+    <t>p_TJ10</t>
+  </si>
+  <si>
+    <t>e_TJ10*</t>
+  </si>
+  <si>
+    <t>p_TJ26</t>
+  </si>
+  <si>
+    <t>e_TJ26*</t>
+  </si>
+  <si>
+    <t>rez_spv_001</t>
+  </si>
+  <si>
+    <t>elc_spv_001</t>
+  </si>
+  <si>
+    <t>rez_spv_002</t>
+  </si>
+  <si>
+    <t>elc_spv_002</t>
+  </si>
+  <si>
+    <t>rez_spv_003</t>
+  </si>
+  <si>
+    <t>elc_spv_003</t>
+  </si>
+  <si>
+    <t>rez_spv_004</t>
+  </si>
+  <si>
+    <t>elc_spv_004</t>
+  </si>
+  <si>
+    <t>rez_spv_005</t>
+  </si>
+  <si>
+    <t>elc_spv_005</t>
+  </si>
+  <si>
+    <t>rez_spv_006</t>
+  </si>
+  <si>
+    <t>elc_spv_006</t>
+  </si>
+  <si>
+    <t>rez_spv_007</t>
+  </si>
+  <si>
+    <t>elc_spv_007</t>
+  </si>
+  <si>
+    <t>rez_spv_008</t>
+  </si>
+  <si>
+    <t>elc_spv_008</t>
+  </si>
+  <si>
+    <t>rez_spv_009</t>
+  </si>
+  <si>
+    <t>elc_spv_009</t>
+  </si>
+  <si>
+    <t>rez_spv_010</t>
+  </si>
+  <si>
+    <t>elc_spv_010</t>
+  </si>
+  <si>
+    <t>rez_won_001</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>rez_won_002</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>rez_won_003</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>rez_won_004</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>rez_won_005</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
   </si>
 </sst>
 </file>
@@ -1168,6 +1355,427 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDFE71D4-B365-437D-A313-2D6EB04726A4}">
+  <dimension ref="B9:E38"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" t="s">
+        <v>101</v>
+      </c>
+      <c r="E10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D11" t="s">
+        <v>104</v>
+      </c>
+      <c r="E11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B12" t="s">
+        <v>106</v>
+      </c>
+      <c r="C12" t="s">
+        <v>107</v>
+      </c>
+      <c r="D12" t="s">
+        <v>107</v>
+      </c>
+      <c r="E12" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B13" t="s">
+        <v>108</v>
+      </c>
+      <c r="C13" t="s">
+        <v>109</v>
+      </c>
+      <c r="D13" t="s">
+        <v>109</v>
+      </c>
+      <c r="E13" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B14" t="s">
+        <v>110</v>
+      </c>
+      <c r="C14" t="s">
+        <v>111</v>
+      </c>
+      <c r="D14" t="s">
+        <v>111</v>
+      </c>
+      <c r="E14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B15" t="s">
+        <v>112</v>
+      </c>
+      <c r="C15" t="s">
+        <v>113</v>
+      </c>
+      <c r="D15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B16" t="s">
+        <v>114</v>
+      </c>
+      <c r="C16" t="s">
+        <v>115</v>
+      </c>
+      <c r="D16" t="s">
+        <v>115</v>
+      </c>
+      <c r="E16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B17" t="s">
+        <v>116</v>
+      </c>
+      <c r="C17" t="s">
+        <v>117</v>
+      </c>
+      <c r="D17" t="s">
+        <v>117</v>
+      </c>
+      <c r="E17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B18" t="s">
+        <v>118</v>
+      </c>
+      <c r="C18" t="s">
+        <v>119</v>
+      </c>
+      <c r="D18" t="s">
+        <v>119</v>
+      </c>
+      <c r="E18" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B19" t="s">
+        <v>120</v>
+      </c>
+      <c r="C19" t="s">
+        <v>121</v>
+      </c>
+      <c r="D19" t="s">
+        <v>121</v>
+      </c>
+      <c r="E19" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B20" t="s">
+        <v>122</v>
+      </c>
+      <c r="C20" t="s">
+        <v>123</v>
+      </c>
+      <c r="D20" t="s">
+        <v>123</v>
+      </c>
+      <c r="E20" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B21" t="s">
+        <v>124</v>
+      </c>
+      <c r="C21" t="s">
+        <v>125</v>
+      </c>
+      <c r="D21" t="s">
+        <v>125</v>
+      </c>
+      <c r="E21" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B22" t="s">
+        <v>126</v>
+      </c>
+      <c r="C22" t="s">
+        <v>127</v>
+      </c>
+      <c r="D22" t="s">
+        <v>127</v>
+      </c>
+      <c r="E22" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B23" t="s">
+        <v>128</v>
+      </c>
+      <c r="C23" t="s">
+        <v>129</v>
+      </c>
+      <c r="D23" t="s">
+        <v>129</v>
+      </c>
+      <c r="E23" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B24" t="s">
+        <v>130</v>
+      </c>
+      <c r="C24" t="s">
+        <v>131</v>
+      </c>
+      <c r="D24" t="s">
+        <v>131</v>
+      </c>
+      <c r="E24" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B25" t="s">
+        <v>132</v>
+      </c>
+      <c r="C25" t="s">
+        <v>133</v>
+      </c>
+      <c r="D25" t="s">
+        <v>133</v>
+      </c>
+      <c r="E25" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B26" t="s">
+        <v>134</v>
+      </c>
+      <c r="C26" t="s">
+        <v>135</v>
+      </c>
+      <c r="D26" t="s">
+        <v>135</v>
+      </c>
+      <c r="E26" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B27" t="s">
+        <v>136</v>
+      </c>
+      <c r="C27" t="s">
+        <v>137</v>
+      </c>
+      <c r="D27" t="s">
+        <v>137</v>
+      </c>
+      <c r="E27" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B28" t="s">
+        <v>138</v>
+      </c>
+      <c r="C28" t="s">
+        <v>139</v>
+      </c>
+      <c r="D28" t="s">
+        <v>139</v>
+      </c>
+      <c r="E28" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B29" t="s">
+        <v>140</v>
+      </c>
+      <c r="C29" t="s">
+        <v>141</v>
+      </c>
+      <c r="D29" t="s">
+        <v>141</v>
+      </c>
+      <c r="E29" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B30" t="s">
+        <v>142</v>
+      </c>
+      <c r="C30" t="s">
+        <v>143</v>
+      </c>
+      <c r="D30" t="s">
+        <v>143</v>
+      </c>
+      <c r="E30" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B31" t="s">
+        <v>144</v>
+      </c>
+      <c r="C31" t="s">
+        <v>145</v>
+      </c>
+      <c r="D31" t="s">
+        <v>145</v>
+      </c>
+      <c r="E31" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B32" t="s">
+        <v>146</v>
+      </c>
+      <c r="C32" t="s">
+        <v>147</v>
+      </c>
+      <c r="D32" t="s">
+        <v>147</v>
+      </c>
+      <c r="E32" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B33" t="s">
+        <v>148</v>
+      </c>
+      <c r="C33" t="s">
+        <v>149</v>
+      </c>
+      <c r="D33" t="s">
+        <v>149</v>
+      </c>
+      <c r="E33" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B34" t="s">
+        <v>150</v>
+      </c>
+      <c r="C34" t="s">
+        <v>151</v>
+      </c>
+      <c r="D34" t="s">
+        <v>151</v>
+      </c>
+      <c r="E34" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B35" t="s">
+        <v>152</v>
+      </c>
+      <c r="C35" t="s">
+        <v>153</v>
+      </c>
+      <c r="D35" t="s">
+        <v>153</v>
+      </c>
+      <c r="E35" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B36" t="s">
+        <v>154</v>
+      </c>
+      <c r="C36" t="s">
+        <v>155</v>
+      </c>
+      <c r="D36" t="s">
+        <v>155</v>
+      </c>
+      <c r="E36" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B37" t="s">
+        <v>156</v>
+      </c>
+      <c r="C37" t="s">
+        <v>157</v>
+      </c>
+      <c r="D37" t="s">
+        <v>157</v>
+      </c>
+      <c r="E37" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B38" t="s">
+        <v>158</v>
+      </c>
+      <c r="C38" t="s">
+        <v>159</v>
+      </c>
+      <c r="D38" t="s">
+        <v>159</v>
+      </c>
+      <c r="E38" t="s">
+        <v>105</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71754C8A-E599-4286-919F-11B5789CC171}">
   <dimension ref="A1:K48"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
